--- a/src/main/resources/espacios/0 Step/0 - Both, Neither.xlsx
+++ b/src/main/resources/espacios/0 Step/0 - Both, Neither.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Both" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="270">
   <si>
     <t xml:space="preserve">On Both</t>
   </si>
@@ -913,7 +913,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -932,10 +932,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1342,6 +1338,9 @@
       <c r="D20" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -1894,16 +1893,16 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="62.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="70.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="69.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="62.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="69.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1911,212 +1910,212 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2139,230 +2138,230 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="54.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="56.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="56.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56.96"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F1" s="5"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
